--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001Out.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001Out.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -24,19 +24,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>登记银行代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>总行机构代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>是否理财子公司</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>社会信用代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中债登记机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人行登记机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -151,7 +151,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -193,7 +193,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -228,7 +228,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -455,16 +455,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.15">

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001Out.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/SysInstRegBankCode001Out.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="机构登记银行代码" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>机构代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -33,6 +33,10 @@
   </si>
   <si>
     <t>中债登记机构代码</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>所属银保监局</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -437,17 +441,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F114"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:G114"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.25" style="1" customWidth="1"/>
-    <col min="2" max="3" width="27.625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="20.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="27.625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.26953125" style="1" customWidth="1"/>
+    <col min="2" max="3" width="27.6328125" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.90625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="27.6328125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:7" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -458,7 +463,7 @@
         <v>4</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -466,8 +471,11 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -475,7 +483,7 @@
       <c r="E2" s="3"/>
       <c r="F2" s="3"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -483,7 +491,7 @@
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
@@ -491,7 +499,7 @@
       <c r="E4" s="3"/>
       <c r="F4" s="3"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -499,7 +507,7 @@
       <c r="E5" s="3"/>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
@@ -507,7 +515,7 @@
       <c r="E6" s="3"/>
       <c r="F6" s="3"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="3"/>
@@ -515,7 +523,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -523,7 +531,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -531,7 +539,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -539,7 +547,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -547,7 +555,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -555,7 +563,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -563,7 +571,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -571,7 +579,7 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -579,7 +587,7 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -587,7 +595,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -595,7 +603,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -603,7 +611,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -611,7 +619,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -619,7 +627,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -627,7 +635,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="3"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -635,7 +643,7 @@
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -643,7 +651,7 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -651,7 +659,7 @@
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -659,7 +667,7 @@
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -667,7 +675,7 @@
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -675,7 +683,7 @@
       <c r="E27" s="3"/>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -683,7 +691,7 @@
       <c r="E28" s="3"/>
       <c r="F28" s="3"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -691,7 +699,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -699,7 +707,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="3"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -707,7 +715,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -715,7 +723,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="3"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -723,7 +731,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -731,7 +739,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="3"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -739,7 +747,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="3"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -747,7 +755,7 @@
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -755,7 +763,7 @@
       <c r="E37" s="3"/>
       <c r="F37" s="3"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -763,7 +771,7 @@
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -771,7 +779,7 @@
       <c r="E39" s="3"/>
       <c r="F39" s="3"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -779,7 +787,7 @@
       <c r="E40" s="3"/>
       <c r="F40" s="3"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -787,7 +795,7 @@
       <c r="E41" s="3"/>
       <c r="F41" s="3"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -795,7 +803,7 @@
       <c r="E42" s="3"/>
       <c r="F42" s="3"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -803,7 +811,7 @@
       <c r="E43" s="3"/>
       <c r="F43" s="3"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -811,7 +819,7 @@
       <c r="E44" s="3"/>
       <c r="F44" s="3"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -819,7 +827,7 @@
       <c r="E45" s="3"/>
       <c r="F45" s="3"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -827,7 +835,7 @@
       <c r="E46" s="3"/>
       <c r="F46" s="3"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -835,7 +843,7 @@
       <c r="E47" s="3"/>
       <c r="F47" s="3"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -843,7 +851,7 @@
       <c r="E48" s="3"/>
       <c r="F48" s="3"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -851,7 +859,7 @@
       <c r="E49" s="3"/>
       <c r="F49" s="3"/>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -859,7 +867,7 @@
       <c r="E50" s="3"/>
       <c r="F50" s="3"/>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -867,7 +875,7 @@
       <c r="E51" s="3"/>
       <c r="F51" s="3"/>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -875,7 +883,7 @@
       <c r="E52" s="3"/>
       <c r="F52" s="3"/>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -883,7 +891,7 @@
       <c r="E53" s="3"/>
       <c r="F53" s="3"/>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -891,7 +899,7 @@
       <c r="E54" s="3"/>
       <c r="F54" s="3"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -899,7 +907,7 @@
       <c r="E55" s="3"/>
       <c r="F55" s="3"/>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -907,7 +915,7 @@
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -915,7 +923,7 @@
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -923,7 +931,7 @@
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -931,7 +939,7 @@
       <c r="E59" s="3"/>
       <c r="F59" s="3"/>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -939,7 +947,7 @@
       <c r="E60" s="3"/>
       <c r="F60" s="3"/>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -947,7 +955,7 @@
       <c r="E61" s="3"/>
       <c r="F61" s="3"/>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -955,7 +963,7 @@
       <c r="E62" s="3"/>
       <c r="F62" s="3"/>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -963,7 +971,7 @@
       <c r="E63" s="3"/>
       <c r="F63" s="3"/>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -971,7 +979,7 @@
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -979,7 +987,7 @@
       <c r="E65" s="3"/>
       <c r="F65" s="3"/>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -987,7 +995,7 @@
       <c r="E66" s="3"/>
       <c r="F66" s="3"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -995,7 +1003,7 @@
       <c r="E67" s="3"/>
       <c r="F67" s="3"/>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -1003,7 +1011,7 @@
       <c r="E68" s="3"/>
       <c r="F68" s="3"/>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -1011,7 +1019,7 @@
       <c r="E69" s="3"/>
       <c r="F69" s="3"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -1019,7 +1027,7 @@
       <c r="E70" s="3"/>
       <c r="F70" s="3"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -1027,7 +1035,7 @@
       <c r="E71" s="3"/>
       <c r="F71" s="3"/>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -1035,7 +1043,7 @@
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -1043,7 +1051,7 @@
       <c r="E73" s="3"/>
       <c r="F73" s="3"/>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -1051,7 +1059,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -1059,7 +1067,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="3"/>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -1067,7 +1075,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="3"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -1075,7 +1083,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -1083,7 +1091,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -1091,7 +1099,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -1099,7 +1107,7 @@
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -1107,7 +1115,7 @@
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -1115,7 +1123,7 @@
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -1123,7 +1131,7 @@
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -1131,7 +1139,7 @@
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -1139,7 +1147,7 @@
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -1147,7 +1155,7 @@
       <c r="E86" s="3"/>
       <c r="F86" s="3"/>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -1155,7 +1163,7 @@
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -1163,7 +1171,7 @@
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -1171,7 +1179,7 @@
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -1179,7 +1187,7 @@
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -1187,7 +1195,7 @@
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -1195,7 +1203,7 @@
       <c r="E92" s="3"/>
       <c r="F92" s="3"/>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -1203,7 +1211,7 @@
       <c r="E93" s="3"/>
       <c r="F93" s="3"/>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -1211,7 +1219,7 @@
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -1219,7 +1227,7 @@
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -1227,7 +1235,7 @@
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -1235,7 +1243,7 @@
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -1243,7 +1251,7 @@
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -1251,7 +1259,7 @@
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -1259,7 +1267,7 @@
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -1267,7 +1275,7 @@
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -1275,7 +1283,7 @@
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -1283,7 +1291,7 @@
       <c r="E103" s="3"/>
       <c r="F103" s="3"/>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -1291,7 +1299,7 @@
       <c r="E104" s="3"/>
       <c r="F104" s="3"/>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -1299,7 +1307,7 @@
       <c r="E105" s="3"/>
       <c r="F105" s="3"/>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -1307,7 +1315,7 @@
       <c r="E106" s="3"/>
       <c r="F106" s="3"/>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -1315,7 +1323,7 @@
       <c r="E107" s="3"/>
       <c r="F107" s="3"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -1323,7 +1331,7 @@
       <c r="E108" s="3"/>
       <c r="F108" s="3"/>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -1331,7 +1339,7 @@
       <c r="E109" s="3"/>
       <c r="F109" s="3"/>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -1339,7 +1347,7 @@
       <c r="E110" s="3"/>
       <c r="F110" s="3"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -1347,7 +1355,7 @@
       <c r="E111" s="3"/>
       <c r="F111" s="3"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -1355,7 +1363,7 @@
       <c r="E112" s="3"/>
       <c r="F112" s="3"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -1363,7 +1371,7 @@
       <c r="E113" s="3"/>
       <c r="F113" s="3"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -1374,6 +1382,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>